--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-02-2026.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£10.48</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£12.15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£15.26</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£15.86</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£19.75</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£22.06</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£25.47</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£33.99</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£33.38</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£40.99</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£42.35</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£40.68</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£779.88</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£26.85</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-pl4000-thermal-laminate-insulation-board?variant=55597627408768 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>£35.65</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationuk.co.uk', port=443): Max retries exceeded with url: /products/625mm-celotex-pl4050-pir-insulated-plasterboard-2400mm-x-1200mm-625mm (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/celotex-cavitywall-85mm</t>
+          <t>£925.79</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£925.79</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/thermaclass-cavity-wall-21?variant=40086149333185</t>
+          <t>£1,202.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
